--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260929.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260929.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>121,976,256</t>
+          <t>30,477,463</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>30,477,463</t>
+          <t>121,976,256</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>25,334,022</t>
+          <t>22,430,583</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>22,430,583</t>
+          <t>25,334,022</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
